--- a/data/2nd Round/Corrected/Mo_125Se_300Sb_Results Table.xlsx
+++ b/data/2nd Round/Corrected/Mo_125Se_300Sb_Results Table.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Corrected Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -507,6 +506,16 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Rseriescm2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Rshuntcm2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -547,9 +556,6 @@
       <c r="L2" t="n">
         <v>0.0002073</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>14.821</v>
       </c>
@@ -563,6 +569,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S2" t="n">
+        <v>7.452048739397593</v>
+      </c>
+      <c r="T2" t="n">
+        <v>18.24605655563812</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -603,9 +615,6 @@
       <c r="L3" t="n">
         <v>0.00014367</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>14.552</v>
       </c>
@@ -619,6 +628,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S3" t="n">
+        <v>7.273261063004898</v>
+      </c>
+      <c r="T3" t="n">
+        <v>12.41589014691165</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -659,9 +674,6 @@
       <c r="L4" t="n">
         <v>0.00013985</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>14.552</v>
       </c>
@@ -675,6 +687,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S4" t="n">
+        <v>7.831567092038285</v>
+      </c>
+      <c r="T4" t="n">
+        <v>11.03759514746235</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -715,9 +733,6 @@
       <c r="L5" t="n">
         <v>0.00023617</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>14.565</v>
       </c>
@@ -731,6 +746,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S5" t="n">
+        <v>7.252718840686287</v>
+      </c>
+      <c r="T5" t="n">
+        <v>19.40409801426029</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -771,9 +792,6 @@
       <c r="L6" t="n">
         <v>0.00042942</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>14.563</v>
       </c>
@@ -787,6 +805,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S6" t="n">
+        <v>10.69755018149334</v>
+      </c>
+      <c r="T6" t="n">
+        <v>27.73484522453987</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -827,9 +851,6 @@
       <c r="L7" t="n">
         <v>0.00028916</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>14.821</v>
       </c>
@@ -843,6 +864,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S7" t="n">
+        <v>13.50657641735543</v>
+      </c>
+      <c r="T7" t="n">
+        <v>21.23107982455874</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -883,9 +910,6 @@
       <c r="L8" t="n">
         <v>0.00049065</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>14.829</v>
       </c>
@@ -899,6 +923,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S8" t="n">
+        <v>9.165517387776321</v>
+      </c>
+      <c r="T8" t="n">
+        <v>51.71492569933881</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -939,9 +969,6 @@
       <c r="L9" t="n">
         <v>0.00022026</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>14.802</v>
       </c>
@@ -955,6 +982,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S9" t="n">
+        <v>7.680049291238374</v>
+      </c>
+      <c r="T9" t="n">
+        <v>44.61438537560322</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -995,9 +1028,6 @@
       <c r="L10" t="n">
         <v>0.00020406</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>14.563</v>
       </c>
@@ -1011,6 +1041,12 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S10" t="n">
+        <v>9.584339229488668</v>
+      </c>
+      <c r="T10" t="n">
+        <v>24.9714934880118</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1051,9 +1087,6 @@
       <c r="L11" t="n">
         <v>4.721e-05</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>14.549</v>
       </c>
@@ -1067,7 +1100,14 @@
           <t>08/21/2026</t>
         </is>
       </c>
-    </row>
+      <c r="S11" t="n">
+        <v>6.550796017659485</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6.766725479922811</v>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
